--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/KANSAS_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/KANSAS_2022.xlsx
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C116">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C175">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C412">
